--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008439271833561955</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18837474</v>
+        <v>4441490</v>
       </c>
       <c r="L2" t="n">
-        <v>11535254</v>
+        <v>2549507</v>
       </c>
       <c r="M2" t="n">
-        <v>2995322</v>
+        <v>625486</v>
       </c>
       <c r="N2" t="n">
-        <v>175168</v>
+        <v>30622</v>
       </c>
       <c r="O2" t="n">
-        <v>1770650</v>
+        <v>384441</v>
       </c>
       <c r="P2" t="n">
-        <v>698063</v>
+        <v>157809</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999982714653015</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9410833120346069</v>
+        <v>0.8879659175872803</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8607800602912903</v>
+        <v>0.759976327419281</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8345198035240173</v>
+        <v>0.69805508852005</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6931554079055786</v>
+        <v>0.4878600537776947</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8689278960227966</v>
+        <v>0.754621148109436</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9077695608139038</v>
+        <v>0.822924792766571</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023734838753813</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>18837474</v>
+        <v>4441490</v>
       </c>
       <c r="E3" t="n">
-        <v>1269018</v>
+        <v>571468</v>
       </c>
       <c r="F3" t="n">
-        <v>15406</v>
+        <v>8817</v>
       </c>
       <c r="G3" t="n">
-        <v>2367</v>
+        <v>1027</v>
       </c>
       <c r="H3" t="n">
-        <v>654</v>
+        <v>409</v>
       </c>
       <c r="I3" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>40066444</v>
+        <v>10016613</v>
       </c>
       <c r="K3" t="n">
-        <v>44014109</v>
+        <v>10745991</v>
       </c>
       <c r="L3" t="n">
-        <v>50404974</v>
+        <v>12255501</v>
       </c>
       <c r="M3" t="n">
-        <v>60996569</v>
+        <v>15126454</v>
       </c>
       <c r="N3" t="n">
-        <v>64884468</v>
+        <v>16208263</v>
       </c>
       <c r="O3" t="n">
-        <v>63014995</v>
+        <v>15695214</v>
       </c>
       <c r="P3" t="n">
-        <v>64474284</v>
+        <v>16102297</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.936025083065033</v>
+        <v>0.8841902017593384</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8840799927711487</v>
+        <v>0.7799311876296997</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8034927248954773</v>
+        <v>0.670697033405304</v>
       </c>
       <c r="U3" t="n">
-        <v>0.491507887840271</v>
+        <v>0.343330591917038</v>
       </c>
       <c r="V3" t="n">
-        <v>0.869536817073822</v>
+        <v>0.7547263503074646</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9028326869010925</v>
+        <v>0.8161999583244324</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1114623</v>
+        <v>532763</v>
       </c>
       <c r="E4" t="n">
-        <v>11535254</v>
+        <v>2549507</v>
       </c>
       <c r="F4" t="n">
-        <v>367841</v>
+        <v>168047</v>
       </c>
       <c r="G4" t="n">
-        <v>8346</v>
+        <v>4497</v>
       </c>
       <c r="H4" t="n">
-        <v>20263</v>
+        <v>13047</v>
       </c>
       <c r="I4" t="n">
-        <v>1422</v>
+        <v>1026</v>
       </c>
       <c r="J4" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>1179324</v>
+        <v>560380</v>
       </c>
       <c r="L4" t="n">
-        <v>1865677</v>
+        <v>805212</v>
       </c>
       <c r="M4" t="n">
-        <v>593954</v>
+        <v>270555</v>
       </c>
       <c r="N4" t="n">
-        <v>77543</v>
+        <v>32146</v>
       </c>
       <c r="O4" t="n">
-        <v>267091</v>
+        <v>125008</v>
       </c>
       <c r="P4" t="n">
-        <v>70924</v>
+        <v>33957</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999991059303284</v>
+        <v>0.9999992847442627</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9385474324226379</v>
+        <v>0.8860740065574646</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8722744584083557</v>
+        <v>0.7698244452476501</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8187124133110046</v>
+        <v>0.6841026544570923</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5751699209213257</v>
+        <v>0.40302973985672</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8692322373390198</v>
+        <v>0.7546737790107727</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9052944183349609</v>
+        <v>0.8195485472679138</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>37372</v>
+        <v>16555</v>
       </c>
       <c r="E5" t="n">
-        <v>501512</v>
+        <v>201943</v>
       </c>
       <c r="F5" t="n">
-        <v>2995322</v>
+        <v>625486</v>
       </c>
       <c r="G5" t="n">
-        <v>35305</v>
+        <v>14196</v>
       </c>
       <c r="H5" t="n">
-        <v>150253</v>
+        <v>69273</v>
       </c>
       <c r="I5" t="n">
-        <v>8113</v>
+        <v>5138</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1287493</v>
+        <v>581739</v>
       </c>
       <c r="L5" t="n">
-        <v>1512495</v>
+        <v>719380</v>
       </c>
       <c r="M5" t="n">
-        <v>732555</v>
+        <v>307105</v>
       </c>
       <c r="N5" t="n">
-        <v>181221</v>
+        <v>58569</v>
       </c>
       <c r="O5" t="n">
-        <v>265664</v>
+        <v>124937</v>
       </c>
       <c r="P5" t="n">
-        <v>75129</v>
+        <v>35537</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999993443489075</v>
+        <v>0.999999463558197</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9622339606285095</v>
+        <v>0.9300583600997925</v>
       </c>
       <c r="S5" t="n">
-        <v>0.948281466960907</v>
+        <v>0.9066362977027893</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9796916246414185</v>
+        <v>0.9646250009536743</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9960384368896484</v>
+        <v>0.994444727897644</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9918437004089355</v>
+        <v>0.9846937656402588</v>
       </c>
       <c r="W5" t="n">
-        <v>0.997763991355896</v>
+        <v>0.9957442879676819</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>27157</v>
+        <v>11005</v>
       </c>
       <c r="E6" t="n">
-        <v>75542</v>
+        <v>18571</v>
       </c>
       <c r="F6" t="n">
-        <v>48795</v>
+        <v>17210</v>
       </c>
       <c r="G6" t="n">
-        <v>175168</v>
+        <v>30622</v>
       </c>
       <c r="H6" t="n">
-        <v>27426</v>
+        <v>10649</v>
       </c>
       <c r="I6" t="n">
-        <v>2279</v>
+        <v>1131</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>18657</v>
+        <v>12636</v>
       </c>
       <c r="F7" t="n">
-        <v>157862</v>
+        <v>73970</v>
       </c>
       <c r="G7" t="n">
-        <v>29998</v>
+        <v>11659</v>
       </c>
       <c r="H7" t="n">
-        <v>1770650</v>
+        <v>384441</v>
       </c>
       <c r="I7" t="n">
-        <v>59071</v>
+        <v>26647</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>948</v>
+        <v>594</v>
       </c>
       <c r="F8" t="n">
-        <v>4050</v>
+        <v>2511</v>
       </c>
       <c r="G8" t="n">
-        <v>1527</v>
+        <v>767</v>
       </c>
       <c r="H8" t="n">
-        <v>68495</v>
+        <v>31630</v>
       </c>
       <c r="I8" t="n">
-        <v>698063</v>
+        <v>157809</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
